--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="D3">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>426</v>
